--- a/data/trans_bre/P1412-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1412-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-74,38%</t>
+          <t>-69,82%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,11</t>
+          <t>-2,19; 1,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,71</t>
+          <t>-1,56; 0,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,14</t>
+          <t>-1,42; 0,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-34,21%</t>
+          <t>-37,45%</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,07</t>
+          <t>-0,61; 1,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,64</t>
+          <t>-1,62; 0,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,46</t>
+          <t>-1,33; 0,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 264,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 206,91</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-28,32%</t>
+          <t>-28,25%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,0</t>
+          <t>-1,72; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,87</t>
+          <t>-1,73; 0,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,8; 165,54</t>
+          <t>-76,96; 166,74</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-1,73</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-95,45%</t>
+          <t>-94,43%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,37</t>
+          <t>-0,64; 2,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,04</t>
+          <t>-1,73; 1,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,11; -0,7</t>
+          <t>-3,85; -0,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,53; —</t>
+          <t>-79,14; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 486,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -49,57</t>
+          <t>-100,0; -41,22</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -0,09</t>
+          <t>-6,1; -0,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,0</t>
+          <t>-1,64; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-57,22%</t>
+          <t>-59,56%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,0</t>
+          <t>-2,4; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,22</t>
+          <t>-2,48; 0,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-89,96; 55,94</t>
+          <t>-89,83; 40,49</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-51,04%</t>
+          <t>-20,63%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,84</t>
+          <t>-1,02; 0,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,62</t>
+          <t>-0,77; 1,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,2</t>
+          <t>-1,3; 0,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-84,99; 352,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 663,18</t>
+          <t>-71,8; 603,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-87,54; 54,71</t>
+          <t>-73,23; 126,32</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,7</t>
+          <t>-0,82; 0,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,34</t>
+          <t>-1,08; 0,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,87</t>
+          <t>-0,46; 0,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 492,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 133,3</t>
+          <t>-88,56; 201,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,67; 881,2</t>
+          <t>-73,94; 501,01</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-43,8%</t>
+          <t>-39,28%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,46</t>
+          <t>-0,4; 0,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,17</t>
+          <t>-0,61; 0,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; -0,03</t>
+          <t>-0,76; -0,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 101,59</t>
+          <t>-45,05; 96,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-64,42; 38,21</t>
+          <t>-63,37; 35,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -2,68</t>
+          <t>-62,68; -3,27</t>
         </is>
       </c>
     </row>
